--- a/artfynd/A 16766-2022 artfynd.xlsx
+++ b/artfynd/A 16766-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16766-2022 artfynd.xlsx
+++ b/artfynd/A 16766-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2459637</v>
+        <v>86651711</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>219955</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kyrkudden, 200 m NNO om, Dls</t>
+          <t>Hedane kapell, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356135.5125264414</v>
+        <v>356190</v>
       </c>
       <c r="R2" t="n">
-        <v>6570212.023487389</v>
+        <v>6570140</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,38 +771,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig blandskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Tomas Janson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Eriksson</t>
+          <t>Tomas Janson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86651711</v>
+        <v>89317916</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,27 +823,24 @@
           <t>30</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hedane kapell, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356190.225221597</v>
+        <v>356194</v>
       </c>
       <c r="R3" t="n">
-        <v>6570139.807131317</v>
+        <v>6570161</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,24 +862,19 @@
           <t>Svanskog</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>S-Säf-0457</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2020-07-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -903,22 +888,127 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Tomas Janson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Tomas Janson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2459637</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kyrkudden, 200 m NNO om, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>356136</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6570212</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-06-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kjell Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kjell Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16766-2022 artfynd.xlsx
+++ b/artfynd/A 16766-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86651711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89317916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2459637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>